--- a/experiment/SwinT2_bestx4/Test/results_table.xlsx
+++ b/experiment/SwinT2_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>31.968/
-0.8892</t>
+          <t>31.998/
+0.8899</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.515/
+          <t>28.516/
 0.7790</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.488/
-0.7337</t>
+          <t>27.509/
+0.7343</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>25.686/
-0.7718</t>
+          <t>25.731/
+0.7737</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.082/
-0.9012</t>
+          <t>30.154/
+0.9023</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.748/
-0.8150</t>
+          <t>28.782/
+0.8158</t>
         </is>
       </c>
     </row>
